--- a/output/pdf_financials_xlsx/AIF.xlsx
+++ b/output/pdf_financials_xlsx/AIF.xlsx
@@ -1222,7 +1222,7 @@
         <v>22.33</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>3.772</v>
+        <v>-23.074</v>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
@@ -1480,25 +1480,25 @@
         <v>14.268</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>109.417</v>
+        <v>-109.417</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-18.439</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>18.194</v>
+        <v>-18.194</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>25.573</v>
+        <v>-25.573</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.889</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>10.232</v>
+        <v>-10.232</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>13.423</v>
+        <v>-13.423</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
@@ -1644,25 +1644,25 @@
         <v>14.268</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>109.417</v>
+        <v>-109.417</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-18.439</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>18.194</v>
+        <v>-18.194</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>25.573</v>
+        <v>-25.573</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.889</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>10.232</v>
+        <v>-10.232</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>13.423</v>
+        <v>-13.423</v>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>37.547368</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>38.39193</v>
+        <v>-38.39193</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>22.33</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>3.772</v>
+        <v>-23.074</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>63.047</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>45.572</v>
+        <v>18.726</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>12.36865647045899</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>9.414243660589785</v>
+        <v>3.868408820947168</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>8.114643976712941</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>255.8589607635207</v>
+        <v>-41.82629799774638</v>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
@@ -2212,25 +2212,25 @@
         <v>3.221560158142748</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>22.95965687570558</v>
+        <v>-22.95965687570558</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-3.612451486886521</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.206471453874148</v>
+        <v>-3.206471453874148</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>4.089147999558673</v>
+        <v>-4.089147999558673</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>-0.120878209425237</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.007329341693282</v>
+        <v>-2.007329341693282</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>2.772917419821309</v>
+        <v>-2.772917419821309</v>
       </c>
       <c r="P32" s="1" t="inlineStr">
         <is>
@@ -5670,25 +5670,25 @@
         <v>14.268</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>109.417</v>
+        <v>-109.417</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-18.439</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>18.194</v>
+        <v>-18.194</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>25.573</v>
+        <v>-25.573</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.889</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10.232</v>
+        <v>-10.232</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>13.423</v>
+        <v>-13.423</v>
       </c>
       <c r="P99" s="1" t="inlineStr">
         <is>
@@ -58403,16 +58403,16 @@
         </is>
       </c>
       <c r="O574" s="5" t="n">
-        <v>25.573</v>
+        <v>-25.573</v>
       </c>
       <c r="P574" s="5" t="n">
         <v>-0.889</v>
       </c>
       <c r="Q574" s="5" t="n">
-        <v>10.232</v>
+        <v>-10.232</v>
       </c>
       <c r="R574" s="5" t="n">
-        <v>13.423</v>
+        <v>-13.423</v>
       </c>
       <c r="S574" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>-18.439</v>
       </c>
       <c r="N612" s="5" t="n">
-        <v>18.194</v>
+        <v>-18.194</v>
       </c>
       <c r="O612" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         </is>
       </c>
       <c r="L627" s="5" t="n">
-        <v>109.417</v>
+        <v>-109.417</v>
       </c>
       <c r="M627" s="5" t="n">
         <v>-18.439</v>

--- a/output/pdf_financials_xlsx/AIF.xlsx
+++ b/output/pdf_financials_xlsx/AIF.xlsx
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>21.585</v>
+        <v>4.226</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>17.898</v>
+        <v>5.883</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>17.182</v>
+        <v>5.194</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>13.515</v>
+        <v>4.917</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>18.321</v>
+        <v>5.841</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>33.04</v>
+        <v>7.017</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>26.197</v>
+        <v>7.233</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>29.184</v>
+        <v>7.26</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>41.025</v>
+        <v>8.089</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>29.995</v>
+        <v>7.838</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>29.017</v>
+        <v>17.565</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>40.995</v>
+        <v>18.53</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>40.717</v>
+        <v>12.676</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>41.8</v>
+        <v>11.977</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>39.548</v>
@@ -2020,37 +2020,37 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>36.458</v>
+        <v>27.86</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>37.026</v>
+        <v>24.546</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>43.137</v>
+        <v>17.114</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>47.276</v>
+        <v>28.312</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>167.045</v>
+        <v>145.121</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>23.228</v>
+        <v>-9.708</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>55.145</v>
+        <v>32.988</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>63.217</v>
+        <v>51.765</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>44.875</v>
+        <v>22.41</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>63.047</v>
+        <v>35.006</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>18.726</v>
+        <v>-11.097</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2080,37 +2080,37 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>12.26864626940006</v>
+        <v>9.375294450202581</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10.88372585215582</v>
+        <v>7.215252383919858</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>10.35918667284643</v>
+        <v>4.109862084036762</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10.67440973061092</v>
+        <v>6.392543537800497</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>35.05210234974673</v>
+        <v>30.45165162140498</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.550681877401167</v>
+        <v>-1.90192955337569</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>9.718636271512032</v>
+        <v>5.813734215697505</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.10846084104722</v>
+        <v>8.27727471149864</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>6.101698141684491</v>
+        <v>3.047109868638427</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>12.36865647045899</v>
+        <v>6.867530388517888</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>3.868408820947168</v>
+        <v>-2.292413365697464</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -5703,49 +5703,49 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.226</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>5.883</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>5.194</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>4.917</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5.841</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>7.017</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>7.233</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>8.089</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>7.838</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>17.565</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>18.53</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>17.223</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>14.499</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>11.559</v>
       </c>
     </row>
     <row r="101">
@@ -6327,25 +6327,25 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>5.417</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.481</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -29777,7 +29777,11 @@
           <t>Depreciation of right-of-use assets 16</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -29860,7 +29864,11 @@
           <t>Depreciation of property, plant and equipment 17</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -33693,7 +33701,11 @@
           <t>Depreciation of right-of-use assets 17</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -33782,7 +33794,11 @@
           <t>Depreciation of property, plant and equipment 18</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -37597,7 +37613,11 @@
           <t>Depreciation of property, plant and equipment 15</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -39929,7 +39949,11 @@
           <t>Depreciation of property, plant and equipment 14</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -42322,7 +42346,11 @@
           <t>Depreciation of property, plant and equipment 13</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -46689,7 +46717,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -47027,7 +47059,11 @@
           <t>Depreciation of property, plant and equipment 15</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E446" s="5" t="n">
         <v>4.226</v>
       </c>
@@ -48896,7 +48932,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -49527,7 +49567,11 @@
           <t>Depreciation of property, plant and equipment 16</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -52557,7 +52601,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -54264,7 +54312,11 @@
           <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E527" s="5" t="n">
         <v>0.123</v>
       </c>
@@ -57103,7 +57155,11 @@
           <t>Depreciation of right-of-use assets 17</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -57192,7 +57248,11 @@
           <t>Depreciation of property, plant and equipment 18</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E561" t="inlineStr">
         <is>
           <t>-</t>
@@ -58966,7 +59026,11 @@
           <t>Depreciation of right-of-use assets 16</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -59053,7 +59117,11 @@
           <t>Depreciation of property, plant and equipment 17</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -60914,7 +60982,11 @@
           <t>Depreciation of property, plant and equipment 15</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -62431,7 +62503,11 @@
           <t>Depreciation of property, plant and equipment 14</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
           <t>-</t>
@@ -63590,7 +63666,11 @@
           <t>Depreciation of property, plant and equipment 13</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>-</t>
@@ -66883,7 +66963,11 @@
           <t>Depreciation of property, plant and equipment 15</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E670" s="5" t="n">
         <v>4.226</v>
       </c>
@@ -68036,7 +68120,11 @@
           <t>Depreciation of property, plant and equipment 16</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E683" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AIF.xlsx
+++ b/output/pdf_financials_xlsx/AIF.xlsx
@@ -1498,12 +1498,10 @@
         <v>-10.232</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-13.423</v>
-      </c>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-11.387</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>-1.222</v>
       </c>
     </row>
     <row r="21">
@@ -1552,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-2.036</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-373.169</v>
       </c>
     </row>
     <row r="22">
@@ -2423,34 +2421,34 @@
         <v>130.67</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>95.96599999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>101.781</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>100.895</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>99.855</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>116.538</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>151.355</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>169.433</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>154.222</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>79.035</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>61.617</v>
       </c>
     </row>
     <row r="38">
@@ -2567,46 +2565,46 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.901</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.112</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.569</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>1.109</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>1.716</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>1.111</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.801</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>1.408</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>6.908</v>
       </c>
     </row>
     <row r="41">
@@ -2619,46 +2617,46 @@
         <v>77.34399999999999</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>102.749</v>
+        <v>103.226</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>105.746</v>
+        <v>107.647</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>109.589</v>
+        <v>110.104</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>130.67</v>
+        <v>131.782</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>97.535</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>102.744</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>102.004</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>100.38</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>118.254</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>152.466</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>172.863</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>155.023</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>80.443</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>68.52500000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2983,46 +2981,46 @@
         <v>0.179</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.417</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.637</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.294</v>
+        <v>0.779</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.425</v>
+        <v>0.313</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>135.328</v>
+        <v>37.793</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>142.55</v>
+        <v>39.806</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>150.368</v>
+        <v>48.364</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>160.797</v>
+        <v>60.417</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>185.807</v>
+        <v>67.553</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>232.463</v>
+        <v>79.997</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>264.611</v>
+        <v>91.748</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>260.671</v>
+        <v>105.648</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>158.839</v>
+        <v>78.396</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>142.138</v>
+        <v>73.613</v>
       </c>
     </row>
     <row r="49">
@@ -3426,31 +3424,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>33.029</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>41.749</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>40.488</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>43.51</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>51.682</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>64.44499999999999</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>61.459</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>66.375</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>71.934</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>0</v>
@@ -3481,28 +3479,28 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>19.504</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>21.825</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>25.297</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>28.81</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>33.667</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>34.812</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>36.001</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>38.737</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
@@ -4001,46 +3999,46 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>38.854</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>34.213</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>37.845</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>44.341</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>3.616</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>7.623</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>10.115</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>7.063</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>11.937</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>20.778</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>20.609</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>20.895</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>19.355</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="68">
@@ -4053,46 +4051,46 @@
         <v>36.468</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>66.36799999999999</v>
+        <v>105.222</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>69.599</v>
+        <v>103.812</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>59.851</v>
+        <v>97.696</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>77.702</v>
+        <v>122.043</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>3.616</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>7.623</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>10.115</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>7.063</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>11.937</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>20.778</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>20.609</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>20.895</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>19.355</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="69">
@@ -4178,25 +4176,25 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>12.564</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>13.914</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>14.856</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>14.346</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>11.009</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="71">
@@ -4230,25 +4228,25 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>12.564</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>13.914</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>14.856</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>14.346</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>11.009</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="72">
@@ -4417,16 +4415,16 @@
         <v>1.314</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>12.097</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>4.456</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>3.857</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>133.59</v>
+        <v>89.249</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -4435,28 +4433,28 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>105.92</v>
+        <v>95.80500000000001</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>125.18</v>
+        <v>117.925</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>283.607</v>
+        <v>259.106</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>209.931</v>
+        <v>175.239</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>239.86</v>
+        <v>204.395</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>218.276</v>
+        <v>183.035</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>230.416</v>
+        <v>200.052</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>559.258</v>
+        <v>527.675</v>
       </c>
     </row>
     <row r="76">
@@ -4718,25 +4716,25 @@
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.0002064582368466573</v>
+        <v>0.000742133662178525</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.1763343454227976</v>
+        <v>0.2112681147331309</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.09660787753041734</v>
+        <v>0.1200976461273282</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.07578141930751663</v>
+        <v>0.1005467851367796</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.05602145594378437</v>
+        <v>0.07983078217603234</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.0433411101390104</v>
+        <v>0.06117753799293607</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.06357926760170504</v>
+        <v>0.08803685527244832</v>
       </c>
     </row>
     <row r="81">
@@ -6119,13 +6117,13 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -6140,10 +6138,10 @@
         <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="K108" s="3" t="n">
         <v>0</v>
@@ -6516,10 +6514,10 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.112</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>3.471</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -7189,25 +7187,25 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
+        <v>-2.482</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0</v>
+        <v>-4.085</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-2.675</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0</v>
+        <v>-2.642</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>-1.269</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>0</v>
@@ -7219,19 +7217,19 @@
         <v>0</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0</v>
+        <v>-0.414</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0</v>
+        <v>-1.898</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="O128" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="P128" s="3" t="n">
-        <v>0</v>
+        <v>-0.949</v>
       </c>
     </row>
     <row r="129">
@@ -7240,10 +7238,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>35.381</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>23.526</v>
@@ -7582,10 +7578,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>12.624</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>12.029</v>
@@ -9558,7 +9552,11 @@
           <t>Lease liabilities 16</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12491,7 +12489,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15137,7 +15139,11 @@
           <t>Lease liabilities 4, 14</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -31960,7 +31966,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E275" s="5" t="n">
         <v>-2.482</v>
       </c>
@@ -36201,7 +36211,11 @@
           <t>Proceeds from disposal of investments 15</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -36996,7 +37010,11 @@
           <t>Proceeds from disposal of investments 14</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -40558,7 +40576,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -51964,7 +51986,11 @@
           <t>Impairment charge 16, 17</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E501" s="5" t="n">
         <v>14</v>
       </c>
@@ -53863,7 +53889,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E522" s="5" t="n">
         <v>17.467</v>
       </c>
@@ -55550,7 +55580,11 @@
           <t>Share of the profit from associates and joint ventures 15</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -55979,7 +56013,11 @@
           <t>Profit (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -56046,7 +56084,7 @@
         </is>
       </c>
       <c r="R546" s="5" t="n">
-        <v>11.387</v>
+        <v>-11.387</v>
       </c>
       <c r="S546" s="5" t="n">
         <v>-1.222</v>
@@ -56064,7 +56102,11 @@
           <t>Profit (loss) from discontinued operations 10</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -56131,10 +56173,10 @@
         </is>
       </c>
       <c r="R547" s="5" t="n">
-        <v>2.036</v>
+        <v>-2.036</v>
       </c>
       <c r="S547" s="5" t="n">
-        <v>373.169</v>
+        <v>-373.169</v>
       </c>
     </row>
     <row r="548">
@@ -63848,7 +63890,11 @@
           <t>Share of (profit) loss of associates 12</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>-</t>
@@ -65274,7 +65320,11 @@
           <t>Share of (profit) loss of associates 13</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E651" t="inlineStr">
         <is>
           <t>-</t>
@@ -67048,7 +67098,11 @@
           <t>Share of (profit) loss of associates 14</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E671" t="inlineStr">
         <is>
           <t>-</t>
@@ -68296,7 +68350,11 @@
           <t>Share of (profit) loss of associates 15</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
           <t>-</t>
@@ -69364,7 +69422,11 @@
           <t>Share of (profit) loss of associate 14</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E697" s="5" t="n">
         <v>1.086</v>
       </c>
